--- a/input/mapping/096. OCB_GOLD_TTDL_FACT_ACCT_ENTRY_Huy.xlsx
+++ b/input/mapping/096. OCB_GOLD_TTDL_FACT_ACCT_ENTRY_Huy.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\OCB\datavault-model\reverse\result\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D543F7DB-3C00-4A15-ADE6-3D9D48CC2857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4BC855A94FF2FA1C1E613D7B656892712431ABED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{974DDACF-9A8A-4C28-AB2B-9639342F4BB3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Script SQL" sheetId="2" r:id="rId2"/>
     <sheet name="FACT_ACCT_ENTRY" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -220,12 +217,13 @@
     <t>Code mới</t>
   </si>
   <si>
-    <t>FACT_ACCT_ENTRY (Gold VIEW)</t>
+    <t>FACT_ACCT_ENTRY (Gold DML — INSERT REPLACE WHERE (truncate-insert theo ngay))</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tcimport;
-CREATE OR REPLACE VIEW FACT_ACCT_ENTRY AS
+INSERT INTO tcimport.FACT_ACCT_ENTRY
+  REPLACE WHERE DATE_COB = TO_DATE(:DATADT,'yyyyMMdd')
 WITH
 -- ===== STS anti-join =====
 br_del AS (
@@ -283,7 +281,7 @@
 teller_ct AS (
     SELECT customer_hashkey, max_by(teller_hashkey, source_event_date) AS teller_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_teller_customer1')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    WHERE source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
 teller_map AS (
@@ -292,7 +290,7 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_teller') ht
     JOIN teller_ct l ON l.teller_hashkey = ht.teller_hashkey
     JOIN cust_dim  cd ON cd.customer_hashkey = l.customer_hashkey
-    WHERE ht.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    WHERE ht.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
       AND ht.business_key LIKE 'TT%'
     GROUP BY ht.business_key
 ),
@@ -710,7 +708,7 @@
 WHERE hub.business_key NOT LIKE 'F%'
   AND xf.t_xref = 'RE.CONSOL.SPEC.ENTRY'
 ;
-</t>
+ </t>
   </si>
   <si>
     <t>LV0 — VIEW đích (FACT_ACCT_ENTRY) — GOLD ZONE C / Databricks (gốc TCIMPORT.FACT_ACCT_ENTRY truncate-insert theo ngày)</t>
@@ -1329,7 +1327,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1471,7 +1469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1502,10 +1500,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1524,6 +1524,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1827,7 +1828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -1838,18 +1839,18 @@
     <col min="7" max="7" width="108" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-    </row>
-    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1863,7 +1864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1">
       <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
@@ -1886,12 +1887,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+    <row r="4" spans="1:7" ht="30" customHeight="1">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1899,12 +1900,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+    <row r="5" spans="1:7" ht="30" customHeight="1">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1912,12 +1913,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+    <row r="6" spans="1:7" ht="30" customHeight="1">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1925,12 +1926,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+    <row r="7" spans="1:7" ht="30" customHeight="1">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1938,12 +1939,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+    <row r="8" spans="1:7" ht="30" customHeight="1">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1951,12 +1952,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+    <row r="9" spans="1:7" ht="30" customHeight="1">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
@@ -1964,49 +1965,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="5"/>
       <c r="C12" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="7"/>
       <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="8"/>
       <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="9"/>
       <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="10"/>
       <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="18"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2024,15 +2025,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -2043,7 +2044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="409.6" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
@@ -2054,17 +2055,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="409.6" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="16" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="4" spans="1:3" ht="409.6" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2073,7 +2075,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
@@ -2082,27 +2084,27 @@
     <col min="6" max="6" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="14" t="s">
         <v>33</v>
       </c>
@@ -2122,7 +2124,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="15" t="s">
         <v>39</v>
       </c>
@@ -2140,7 +2142,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="22.9" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>44</v>
       </c>
@@ -2160,7 +2162,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="15" t="s">
         <v>50</v>
       </c>
@@ -2180,7 +2182,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="15" t="s">
         <v>55</v>
       </c>
@@ -2200,7 +2202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="22.9" customHeight="1">
       <c r="A9" s="15" t="s">
         <v>60</v>
       </c>
@@ -2220,7 +2222,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="22.9" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>66</v>
       </c>
@@ -2240,7 +2242,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="22.9" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>71</v>
       </c>
@@ -2260,7 +2262,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="22.9" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>76</v>
       </c>
@@ -2280,7 +2282,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="15" t="s">
         <v>81</v>
       </c>
@@ -2300,7 +2302,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="22.9" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>86</v>
       </c>
@@ -2320,7 +2322,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="15" t="s">
         <v>91</v>
       </c>
@@ -2340,7 +2342,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="15" t="s">
         <v>96</v>
       </c>
@@ -2360,7 +2362,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="15" t="s">
         <v>101</v>
       </c>
@@ -2380,17 +2382,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-    </row>
-    <row r="20" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+    </row>
+    <row r="20" spans="1:6" ht="26.45" customHeight="1">
       <c r="A20" s="14" t="s">
         <v>107</v>
       </c>
@@ -2410,7 +2412,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="45.6" customHeight="1">
       <c r="A21" s="15" t="s">
         <v>8</v>
       </c>
@@ -2430,7 +2432,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="45.6" customHeight="1">
       <c r="A22" s="15" t="s">
         <v>8</v>
       </c>
@@ -2450,7 +2452,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="45.6" customHeight="1">
       <c r="A23" s="15" t="s">
         <v>8</v>
       </c>
@@ -2470,7 +2472,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="45.6" customHeight="1">
       <c r="A24" s="15" t="s">
         <v>8</v>
       </c>
@@ -2490,7 +2492,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="45.6" customHeight="1">
       <c r="A25" s="15" t="s">
         <v>8</v>
       </c>
@@ -2510,7 +2512,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="45.6" customHeight="1">
       <c r="A26" s="15" t="s">
         <v>8</v>
       </c>
@@ -2530,7 +2532,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="45.6" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>8</v>
       </c>
@@ -2550,7 +2552,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="45.6" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>8</v>
       </c>
@@ -2570,7 +2572,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="45.6" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>8</v>
       </c>
@@ -2590,7 +2592,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="45.6" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>8</v>
       </c>
@@ -2610,7 +2612,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="45.6" customHeight="1">
       <c r="A31" s="15" t="s">
         <v>8</v>
       </c>
@@ -2630,7 +2632,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="45.6" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>8</v>
       </c>
@@ -2650,7 +2652,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="45.6" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>8</v>
       </c>
@@ -2670,7 +2672,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="45.6" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>8</v>
       </c>
@@ -2690,7 +2692,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="45.6" customHeight="1">
       <c r="A35" s="15" t="s">
         <v>8</v>
       </c>
@@ -2710,7 +2712,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="45.6" customHeight="1">
       <c r="A36" s="15" t="s">
         <v>8</v>
       </c>
@@ -2730,7 +2732,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="45.6" customHeight="1">
       <c r="A37" s="15" t="s">
         <v>8</v>
       </c>
@@ -2750,7 +2752,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="45.6" customHeight="1">
       <c r="A38" s="15" t="s">
         <v>8</v>
       </c>
@@ -2770,7 +2772,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="45.6" customHeight="1">
       <c r="A39" s="15" t="s">
         <v>8</v>
       </c>
@@ -2790,7 +2792,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="45.6" customHeight="1">
       <c r="A40" s="15" t="s">
         <v>8</v>
       </c>
@@ -2810,7 +2812,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="45.6" customHeight="1">
       <c r="A41" s="15" t="s">
         <v>8</v>
       </c>
@@ -2830,7 +2832,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="45.6" customHeight="1">
       <c r="A42" s="15" t="s">
         <v>8</v>
       </c>
@@ -2850,7 +2852,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="45.6" customHeight="1">
       <c r="A43" s="15" t="s">
         <v>8</v>
       </c>
@@ -2870,7 +2872,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="45.6" customHeight="1">
       <c r="A44" s="15" t="s">
         <v>8</v>
       </c>
@@ -2890,7 +2892,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="45.6" customHeight="1">
       <c r="A45" s="15" t="s">
         <v>8</v>
       </c>
@@ -2904,14 +2906,14 @@
         <v>133</v>
       </c>
       <c r="E45" s="15" t="e">
-        <f>TRANSACTION_NO (STMT) / our_ref</f>
+        <f ca="1">TRANSACTION_NO (STMT) / our_ref</f>
         <v>#NAME?</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="45.6" customHeight="1">
       <c r="A46" s="15" t="s">
         <v>8</v>
       </c>
@@ -2931,7 +2933,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="45.6" customHeight="1">
       <c r="A47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2951,7 +2953,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="45.6" customHeight="1">
       <c r="A48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2971,7 +2973,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="45.6" customHeight="1">
       <c r="A49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2991,7 +2993,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="45.6" customHeight="1">
       <c r="A50" s="15" t="s">
         <v>8</v>
       </c>
@@ -3011,7 +3013,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="45.6" customHeight="1">
       <c r="A51" s="15" t="s">
         <v>8</v>
       </c>
@@ -3031,7 +3033,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="45.6" customHeight="1">
       <c r="A52" s="15" t="s">
         <v>8</v>
       </c>
@@ -3051,7 +3053,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="45.6" customHeight="1">
       <c r="A53" s="15" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +3073,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="45.6" customHeight="1">
       <c r="A54" s="15" t="s">
         <v>8</v>
       </c>
@@ -3091,7 +3093,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="45.6" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>8</v>
       </c>
@@ -3111,7 +3113,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="45.6" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>8</v>
       </c>
@@ -3131,7 +3133,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="45.6" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>8</v>
       </c>
@@ -3151,7 +3153,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="45.6" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>8</v>
       </c>
@@ -3171,7 +3173,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="45.6" customHeight="1">
       <c r="A59" s="15" t="s">
         <v>8</v>
       </c>
@@ -3191,7 +3193,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="45.6" customHeight="1">
       <c r="A60" s="15" t="s">
         <v>8</v>
       </c>
@@ -3222,6 +3224,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -3393,7 +3405,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3402,24 +3414,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D86A80-510C-4FDA-841D-02F5C134AD8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3596D348-D398-4C59-98CF-9448EC3504C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE76EE12-158D-4A9A-BF37-974D68C545C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53126FA-9F6B-4F92-99EB-0CE29CADC0C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4496DCC-ADF6-4861-8FEA-6B8407FE353B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371E020A-B688-42B8-86E0-2E13076CBCD8}"/>
 </file>